--- a/site/public/ig/CodeSystem-heartland-monitoring-track.xlsx
+++ b/site/public/ig/CodeSystem-heartland-monitoring-track.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T20:13:50-04:00</t>
+    <t>2026-09-17T14:02:25-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/public/ig/CodeSystem-heartland-monitoring-track.xlsx
+++ b/site/public/ig/CodeSystem-heartland-monitoring-track.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T14:02:25-04:00</t>
+    <t>2026-09-17T14:11:14-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/public/ig/CodeSystem-heartland-monitoring-track.xlsx
+++ b/site/public/ig/CodeSystem-heartland-monitoring-track.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,19 +48,19 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T14:11:14-04:00</t>
+    <t>2026-09-29T19:00:36-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Patient-level remote monitoring track assignment from HEARTLAND Protocol v3.2 Module 5. Both tracks follow identical clinical algorithms, differing only in data collection method.</t>
+    <t>Documented monitoring routes with stable Track A and Track B codes. A route does not establish equivalent outcomes, successful contact, device availability or completed monitoring. Clinical requirements are not reduced by the route; access, preference and the supported local plan require separate documentation.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -102,9 +102,6 @@
     <t>Case Sensitive</t>
   </si>
   <si>
-    <t>true</t>
-  </si>
-  <si>
     <t>Value Set (all codes)</t>
   </si>
   <si>
@@ -153,7 +150,7 @@
     <t>Digital Track A</t>
   </si>
   <si>
-    <t>App-based symptom tracking, Bluetooth-enabled devices, automated data transmission.</t>
+    <t>A planned digital route, such as app-based entries. This code alone does not assert Bluetooth devices, automatic transmission or reliable connectivity.</t>
   </si>
   <si>
     <t>analog-track-b</t>
@@ -162,7 +159,7 @@
     <t>Analog Track B</t>
   </si>
   <si>
-    <t>Voice telephone calls, paper symptom diaries, manual data entry by staff.</t>
+    <t>A planned analog route, such as telephone contact and a paper diary. This code alone does not assert telephone access, staff entry, successful contact or review.</t>
   </si>
 </sst>
 </file>
@@ -426,53 +423,53 @@
         <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>34</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>37</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -487,44 +484,44 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>39</v>
       </c>
-      <c r="B1" t="s" s="1">
+      <c r="C1" t="s" s="1">
         <v>40</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>41</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>42</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="C2" t="s" s="2">
+      <c r="D2" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C3" t="s" s="2">
         <v>47</v>
       </c>
-      <c r="C3" t="s" s="2">
+      <c r="D3" t="s" s="2">
         <v>48</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
